--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -367,30 +367,35 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Species_printed</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>CST_termination_grade</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>CM_monosynaptic</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>CM_connection_inference</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>DOI</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Source_location</t>
         </is>
@@ -404,28 +409,33 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Sapajus apella</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>Cebus apella</t>
         </is>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>2</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>likely</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Bortoff &amp; Strick 1993</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>10.1523/JNEUROSCI.13-12-05105.1993</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Abstract; Results pp. 5108-5111; Figures 3, 5-11</t>
         </is>
@@ -442,25 +452,30 @@
           <t>Saimiri sciureus</t>
         </is>
       </c>
-      <c r="C3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Saimiri sciureus</t>
+        </is>
+      </c>
+      <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>against</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Bortoff &amp; Strick 1993</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>10.1523/JNEUROSCI.13-12-05105.1993</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Abstract; Results pp. 5109-5111; Figures 4, 6, 10-11</t>
         </is>
@@ -747,13 +762,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D564CCEB-6430-4009-A265-BC897927170C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BE49FF5-8598-4D6F-B543-CBE2279C6006}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A310F9F0-88F3-497F-BEFD-AFF5D13B89EE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3001EFBB-1DCA-42AD-BAD9-FC8FE284FDC5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F7B53F3-4E4E-441C-ADF5-AF32C4EC414F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37A41FA7-E536-4BEE-A36F-596DD6863765}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -762,13 +762,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BE49FF5-8598-4D6F-B543-CBE2279C6006}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BCE27AA-5CFE-4BE4-8EF0-39CD845FE264}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3001EFBB-1DCA-42AD-BAD9-FC8FE284FDC5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3259F6C6-A575-4603-A7F4-63BA08A39B18}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37A41FA7-E536-4BEE-A36F-596DD6863765}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{813C4564-DF10-407E-8700-A3992BA590DE}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -762,13 +762,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BCE27AA-5CFE-4BE4-8EF0-39CD845FE264}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FFF27F2-602F-4519-995E-7229EB4B7C9D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3259F6C6-A575-4603-A7F4-63BA08A39B18}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3D1E294-69E5-4DDB-9BE6-E918B548ABA0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{813C4564-DF10-407E-8700-A3992BA590DE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9FBFB4C-1858-4318-AB69-F69ECD95ADEA}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -762,13 +762,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FFF27F2-602F-4519-995E-7229EB4B7C9D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{066D64F1-A52C-4552-91DB-CB3591EAD4DC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3D1E294-69E5-4DDB-9BE6-E918B548ABA0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B46D26F2-9E7B-4B85-91CB-1AAEA0427D80}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9FBFB4C-1858-4318-AB69-F69ECD95ADEA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B69E7F2B-EAEC-49B3-8AE8-640230DCF3DE}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -762,13 +762,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{066D64F1-A52C-4552-91DB-CB3591EAD4DC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EF228E9-83FC-4B1C-9621-4E4915DD7EDA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B46D26F2-9E7B-4B85-91CB-1AAEA0427D80}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3EDDFF5-0331-4B8D-8FE3-DE54032DB33F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B69E7F2B-EAEC-49B3-8AE8-640230DCF3DE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4EDE33C-0980-4DB5-A41B-48834FC2D562}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -762,13 +762,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EF228E9-83FC-4B1C-9621-4E4915DD7EDA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12AAAA86-7A0A-4062-8179-76CF9E862934}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3EDDFF5-0331-4B8D-8FE3-DE54032DB33F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{520C7C48-FD91-436B-B929-013CFE1DA30B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4EDE33C-0980-4DB5-A41B-48834FC2D562}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA7A7C2C-C3B0-42C5-80AE-D91ED2985BBF}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -762,13 +762,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12AAAA86-7A0A-4062-8179-76CF9E862934}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A190F143-0F15-40AB-8901-7D61351EAE49}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{520C7C48-FD91-436B-B929-013CFE1DA30B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AB0E02B-5FB1-4D69-893B-C45448D44705}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA7A7C2C-C3B0-42C5-80AE-D91ED2985BBF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C9AB37C-382D-4894-874E-0111C6A6CD36}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -762,13 +762,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A190F143-0F15-40AB-8901-7D61351EAE49}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9464E789-DE24-4EEC-96F4-EF570BCE2E76}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AB0E02B-5FB1-4D69-893B-C45448D44705}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76A36AEA-120E-4AE2-8C5D-920D9ECE3583}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C9AB37C-382D-4894-874E-0111C6A6CD36}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C1A42FE-AAD5-4D49-B6A1-8D8C6246E3CE}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -762,13 +762,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9464E789-DE24-4EEC-96F4-EF570BCE2E76}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB4811D0-61DC-44A2-AE85-9CA07955A6F5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76A36AEA-120E-4AE2-8C5D-920D9ECE3583}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BBA65E0-D801-47F8-8972-4FDAAB0C78E6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C1A42FE-AAD5-4D49-B6A1-8D8C6246E3CE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46DA903E-1541-4307-B098-C42564C18B74}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -762,13 +762,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB4811D0-61DC-44A2-AE85-9CA07955A6F5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71B09043-E3B1-481E-AB24-C1BCE1CAC9EE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BBA65E0-D801-47F8-8972-4FDAAB0C78E6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{435601AD-747D-483F-8803-A6DD4F0FB0E7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46DA903E-1541-4307-B098-C42564C18B74}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AE52E8C-5DF8-47DE-B349-337B198973A7}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -762,13 +762,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71B09043-E3B1-481E-AB24-C1BCE1CAC9EE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22625145-35C4-4B37-B999-730CBA1E6CC9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{435601AD-747D-483F-8803-A6DD4F0FB0E7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47A20D6B-7BAC-4AAE-BE45-C2D6D36ECD16}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AE52E8C-5DF8-47DE-B349-337B198973A7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98E6922B-5010-4898-8876-4405828AFEFF}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinal_terminations.xlsx
+++ b/____EvoM1_TraitTable/corticospinal_terminations.xlsx
@@ -762,13 +762,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22625145-35C4-4B37-B999-730CBA1E6CC9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FB7E848-0A39-4E08-A78E-24C067726463}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47A20D6B-7BAC-4AAE-BE45-C2D6D36ECD16}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CCD6B9B-4E67-4DEE-B0E5-87D5AE4B6529}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98E6922B-5010-4898-8876-4405828AFEFF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86FC9D3C-910D-4D46-840B-ACEC899B90FA}"/>
 </file>